--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us-dev-sandbox\InputData\elec\RAF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB56CAB2-6239-4ED1-B74E-3A7D68FFCF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1956C23D-A95D-41EC-80B7-DB5382AE7087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="3375" windowWidth="21600" windowHeight="12645" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="65">
   <si>
     <t>Source:</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>Update 2026-08-18: natural gas peaker and petroleum RAF set to 0.8 (were 1.0 since 2026-08-17). SYSHECF for these sources calibrates to EIA CF / 0.8 so realized CFs are unchanged at observed EIA levels.</t>
+  </si>
+  <si>
+    <t>Update 2026-09-30: natural gas peaker RAF raised 0.8 -&gt; 0.9, matching gas combined cycle and steam turbines (petroleum stays 0.8). DRAFT rationale, pending Robbie's review: RAF covers deliverability beyond what capacity factors capture, and peakers are typically sited near load, so there is no basis for a larger regional derate than combined cycle. With MCF 0.95 and the 0.98 thermal ELCCAfR, the peaker reliability credit is 0.84, below the NERC GADS 1-EFORd class average for gas turbines (~0.91). SYSHECF-natural-gas-peaker cell AB13 was updated to 0.9 at the same time, so realized peaker CF (SYSHECF x RAF) stays at the observed EIA CF.</t>
   </si>
 </sst>
 </file>
@@ -900,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667665C7-8A8E-46D9-B686-64BA7741F669}">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="73.85546875" customWidth="1"/>
@@ -1087,6 +1090,11 @@
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2107,82 +2115,82 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">

--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\US\Models\eps-us\InputData\elec\RAF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF73A49-FEDC-4BBB-BCB2-03B2ADBAAE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1956C23D-A95D-41EC-80B7-DB5382AE7087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="65">
   <si>
     <t>Source:</t>
   </si>
@@ -342,6 +342,12 @@
   </si>
   <si>
     <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>Update 2026-08-18: natural gas peaker and petroleum RAF set to 0.8 (were 1.0 since 2026-08-17). SYSHECF for these sources calibrates to EIA CF / 0.8 so realized CFs are unchanged at observed EIA levels.</t>
+  </si>
+  <si>
+    <t>Update 2026-09-30: natural gas peaker RAF raised 0.8 -&gt; 0.9, matching gas combined cycle and steam turbines (petroleum stays 0.8). DRAFT rationale, pending Robbie's review: RAF covers deliverability beyond what capacity factors capture, and peakers are typically sited near load, so there is no basis for a larger regional derate than combined cycle. With MCF 0.95 and the 0.98 thermal ELCCAfR, the peaker reliability credit is 0.84, below the NERC GADS 1-EFORd class average for gas turbines (~0.91). SYSHECF-natural-gas-peaker cell AB13 was updated to 0.9 at the same time, so realized peaker CF (SYSHECF x RAF) stays at the observed EIA CF.</t>
   </si>
 </sst>
 </file>
@@ -351,7 +357,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,9 +607,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -641,7 +647,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -747,7 +753,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -889,7 +895,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -897,28 +903,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667665C7-8A8E-46D9-B686-64BA7741F669}">
-  <dimension ref="A1:B41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="73.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -926,159 +932,169 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1093,12 +1109,12 @@
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:AA25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -1181,7 +1197,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1264,7 +1280,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1347,7 +1363,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -1430,7 +1446,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1513,7 +1529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1596,7 +1612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1679,7 +1695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1762,7 +1778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1845,7 +1861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1928,7 +1944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2011,90 +2027,90 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="C12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="M12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="O12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="P12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="R12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="T12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="U12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="X12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Y12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Z12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AA12">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2177,7 +2193,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2260,7 +2276,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2343,7 +2359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2426,7 +2442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2509,7 +2525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -2592,7 +2608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -2675,7 +2691,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2758,7 +2774,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2841,7 +2857,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -2924,7 +2940,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -3007,90 +3023,90 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>45</v>
       </c>
       <c r="B24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA24">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -3184,13 +3200,13 @@
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.5703125" customWidth="1"/>
     <col min="2" max="2" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>22</v>
       </c>
@@ -3198,7 +3214,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
